--- a/reports/New_External_Dining_Furniture_Details_2026.xlsx
+++ b/reports/New_External_Dining_Furniture_Details_2026.xlsx
@@ -10,7 +10,12 @@
     <sheet name="Mall External Dining" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Store Inventory" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Mall External Dining'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Mall External Dining'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Store Inventory'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Store Inventory'!$A$1:$E$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -719,7 +724,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -968,6 +973,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -976,7 +982,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1106,5 +1112,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>